--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>33773605.37</v>
       </c>
       <c r="C2" t="n">
         <v>485938.81</v>
@@ -471,10 +471,8 @@
       <c r="D2" t="n">
         <v>124014.97</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E2" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="3">
@@ -484,7 +482,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>8860</v>
       </c>
       <c r="C3" t="n">
         <v>187.8</v>
@@ -492,10 +490,8 @@
       <c r="D3" t="n">
         <v>187.8</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2.12</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>33349264.86</v>
       </c>
       <c r="C4" t="n">
         <v>1593750.53</v>
@@ -513,10 +509,8 @@
       <c r="D4" t="n">
         <v>681012.09</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E4" t="n">
+        <v>2.04</v>
       </c>
     </row>
     <row r="5">
@@ -526,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>22291927.7</v>
       </c>
       <c r="C5" t="n">
         <v>948493.37</v>
@@ -534,10 +528,8 @@
       <c r="D5" t="n">
         <v>342778.37</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E5" t="n">
+        <v>1.54</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>27480060.57</v>
       </c>
       <c r="C6" t="n">
         <v>1422050.2</v>
@@ -555,10 +547,8 @@
       <c r="D6" t="n">
         <v>527889.5</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E6" t="n">
+        <v>1.92</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>24252328.49</v>
       </c>
       <c r="C7" t="n">
         <v>1375727.42</v>
@@ -576,10 +566,8 @@
       <c r="D7" t="n">
         <v>506530.73</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="E7" t="n">
+        <v>2.09</v>
       </c>
     </row>
     <row r="8">
@@ -589,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>573098.29</v>
+        <v>25495655.73</v>
       </c>
       <c r="C8" t="n">
         <v>1060008.75</v>
@@ -598,7 +586,7 @@
         <v>459796.7600000001</v>
       </c>
       <c r="E8" t="n">
-        <v>80.23</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -608,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18649197.14</v>
+        <v>20629233.01</v>
       </c>
       <c r="C9" t="n">
         <v>415738.46</v>
@@ -617,7 +605,7 @@
         <v>145880.72</v>
       </c>
       <c r="E9" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6340390.51</v>
+        <v>5895642.84</v>
       </c>
       <c r="C10" t="n">
         <v>3205.38</v>
@@ -636,6 +624,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NaT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>26321210.49</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -466,7 +466,7 @@
         <v>33773605.37</v>
       </c>
       <c r="C2" t="n">
-        <v>485938.81</v>
+        <v>485968.71</v>
       </c>
       <c r="D2" t="n">
         <v>124014.97</v>
@@ -523,7 +523,7 @@
         <v>22291927.7</v>
       </c>
       <c r="C5" t="n">
-        <v>948493.37</v>
+        <v>948838.27</v>
       </c>
       <c r="D5" t="n">
         <v>342778.37</v>
@@ -542,7 +542,7 @@
         <v>27480060.57</v>
       </c>
       <c r="C6" t="n">
-        <v>1422050.2</v>
+        <v>1423314.19</v>
       </c>
       <c r="D6" t="n">
         <v>527889.5</v>
@@ -561,13 +561,13 @@
         <v>24252328.49</v>
       </c>
       <c r="C7" t="n">
-        <v>1375727.42</v>
+        <v>1397613.76</v>
       </c>
       <c r="D7" t="n">
-        <v>506530.73</v>
+        <v>518452.08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="8">
@@ -580,13 +580,13 @@
         <v>25495655.73</v>
       </c>
       <c r="C8" t="n">
-        <v>1060008.75</v>
+        <v>1133555.49</v>
       </c>
       <c r="D8" t="n">
-        <v>459796.7600000001</v>
+        <v>494052.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="9">
@@ -599,13 +599,13 @@
         <v>20629233.01</v>
       </c>
       <c r="C9" t="n">
-        <v>415738.46</v>
+        <v>529816.37</v>
       </c>
       <c r="D9" t="n">
-        <v>145880.72</v>
+        <v>205609.53</v>
       </c>
       <c r="E9" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -618,13 +618,13 @@
         <v>5895642.84</v>
       </c>
       <c r="C10" t="n">
-        <v>3205.38</v>
+        <v>22311.74</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>11632.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -657,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>219376.26</v>
+        <v>220951.31</v>
       </c>
     </row>
     <row r="49">
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>14445.49</v>
+        <v>23648.49</v>
       </c>
     </row>
     <row r="50">
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>63748.22</v>
+        <v>63793.22</v>
       </c>
     </row>
     <row r="52">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>51695.17</v>
+        <v>52213.47</v>
       </c>
     </row>
     <row r="53">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>14630.43</v>
+        <v>15210.43</v>
       </c>
     </row>
     <row r="55">
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>169292.25</v>
+        <v>201578.7</v>
       </c>
     </row>
     <row r="61">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>74245.08</v>
+        <v>74630.58</v>
       </c>
     </row>
     <row r="62">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>116853.62</v>
+        <v>118398.56</v>
       </c>
     </row>
     <row r="63">
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>42904.25</v>
+        <v>42942.7</v>
       </c>
     </row>
     <row r="64">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>19843.3</v>
+        <v>21670.29</v>
       </c>
     </row>
     <row r="69">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>28310.84</v>
+        <v>71256.27</v>
       </c>
     </row>
     <row r="70">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>9672.66</v>
+        <v>16564.71</v>
       </c>
     </row>
     <row r="71">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>59755.18</v>
+        <v>63650.71000000001</v>
       </c>
     </row>
     <row r="72">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>21493.73</v>
+        <v>22462.91</v>
       </c>
     </row>
     <row r="73">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5287.5</v>
+        <v>6826.26</v>
       </c>
     </row>
     <row r="74">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>849.99</v>
+        <v>2510.86</v>
       </c>
     </row>
     <row r="75">
@@ -1785,6 +1785,81 @@
       </c>
       <c r="C75" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FAVORITA</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>6276.88</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1815.59</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>29.95</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3509.9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33773605.37</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>485968.71</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>124014.97</v>
       </c>
       <c r="E2" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8860</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>187.8</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>187.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33349264.86</v>
+        <v>1542456.16</v>
       </c>
       <c r="C4" t="n">
-        <v>1593750.53</v>
+        <v>2153017.43</v>
       </c>
       <c r="D4" t="n">
         <v>681012.09</v>
       </c>
       <c r="E4" t="n">
-        <v>2.04</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +520,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22291927.7</v>
+        <v>3857193.38</v>
       </c>
       <c r="C5" t="n">
-        <v>948838.27</v>
+        <v>2482598.59</v>
       </c>
       <c r="D5" t="n">
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>1.54</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27480060.57</v>
+        <v>3829611.7</v>
       </c>
       <c r="C6" t="n">
-        <v>1423314.19</v>
+        <v>2493334.69</v>
       </c>
       <c r="D6" t="n">
         <v>527889.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1.92</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24252328.49</v>
+        <v>5747075.1</v>
       </c>
       <c r="C7" t="n">
-        <v>1397613.76</v>
+        <v>2261706.61</v>
       </c>
       <c r="D7" t="n">
         <v>518452.08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.14</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25495655.73</v>
+        <v>17756400.59</v>
       </c>
       <c r="C8" t="n">
-        <v>1133555.49</v>
+        <v>1568692.59</v>
       </c>
       <c r="D8" t="n">
         <v>494052.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1.94</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20629233.01</v>
+        <v>36731164.22</v>
       </c>
       <c r="C9" t="n">
-        <v>529816.37</v>
+        <v>1613646.39</v>
       </c>
       <c r="D9" t="n">
         <v>205609.53</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -615,34 +615,110 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5895642.84</v>
+        <v>16611703.23</v>
       </c>
       <c r="C10" t="n">
-        <v>22311.74</v>
+        <v>921426.51</v>
       </c>
       <c r="D10" t="n">
         <v>11632.33</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NaT</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26321210.49</v>
+        <v>4417322.52</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>266298.55</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8395809.18</v>
+      </c>
+      <c r="C12" t="n">
+        <v>120179.81</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6075830.56</v>
+      </c>
+      <c r="C13" t="n">
+        <v>155603.53</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3263554.56</v>
+      </c>
+      <c r="C14" t="n">
+        <v>143993.96</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4468719.48</v>
+      </c>
+      <c r="C15" t="n">
+        <v>153281.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -545,7 +545,7 @@
         <v>2493334.69</v>
       </c>
       <c r="D6" t="n">
-        <v>527889.5</v>
+        <v>527737.6</v>
       </c>
       <c r="E6" t="n">
         <v>13.78</v>
@@ -583,7 +583,7 @@
         <v>1568692.59</v>
       </c>
       <c r="D8" t="n">
-        <v>494052.1</v>
+        <v>493514.7</v>
       </c>
       <c r="E8" t="n">
         <v>2.78</v>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>89036.17</v>
+        <v>88884.27</v>
       </c>
     </row>
     <row r="40">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>201578.7</v>
+        <v>201193.2</v>
       </c>
     </row>
     <row r="61">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>118398.56</v>
+        <v>118246.66</v>
       </c>
     </row>
     <row r="63">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -507,10 +507,10 @@
         <v>2153017.43</v>
       </c>
       <c r="D4" t="n">
-        <v>681012.09</v>
+        <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>44.15</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         <v>2493334.69</v>
       </c>
       <c r="D6" t="n">
-        <v>527737.6</v>
+        <v>527678.1</v>
       </c>
       <c r="E6" t="n">
         <v>13.78</v>
@@ -564,10 +564,10 @@
         <v>2261706.61</v>
       </c>
       <c r="D7" t="n">
-        <v>518452.08</v>
+        <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.02</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="8">
@@ -583,10 +583,10 @@
         <v>1568692.59</v>
       </c>
       <c r="D8" t="n">
-        <v>493514.7</v>
+        <v>509866.83</v>
       </c>
       <c r="E8" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>1613646.39</v>
       </c>
       <c r="D9" t="n">
-        <v>205609.53</v>
+        <v>277912.15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10">
@@ -618,13 +618,13 @@
         <v>16611703.23</v>
       </c>
       <c r="C10" t="n">
-        <v>921426.51</v>
+        <v>1839372.09</v>
       </c>
       <c r="D10" t="n">
-        <v>11632.33</v>
+        <v>37874.32</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>228274.86</v>
+        <v>223997.96</v>
       </c>
     </row>
     <row r="17">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>155030.24</v>
+        <v>154970.74</v>
       </c>
     </row>
     <row r="37">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49110.14</v>
+        <v>50068.36</v>
       </c>
     </row>
     <row r="48">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>220951.31</v>
+        <v>226650.61</v>
       </c>
     </row>
     <row r="49">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>63793.22</v>
+        <v>59516.32</v>
       </c>
     </row>
     <row r="52">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>52213.47</v>
+        <v>52391.37</v>
       </c>
     </row>
     <row r="53">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6371.57</v>
+        <v>6757.07</v>
       </c>
     </row>
     <row r="59">
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>22309.44</v>
+        <v>27222.1</v>
       </c>
     </row>
     <row r="60">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>201193.2</v>
+        <v>214668.87</v>
       </c>
     </row>
     <row r="61">
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>74630.58</v>
+        <v>70353.68000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>118246.66</v>
+        <v>120061.86</v>
       </c>
     </row>
     <row r="63">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1770.01</v>
+        <v>1810.01</v>
       </c>
     </row>
     <row r="66">
@@ -1721,11 +1721,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>317.5</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="67">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>350</v>
+        <v>906.5</v>
       </c>
     </row>
     <row r="68">
@@ -1751,11 +1751,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21670.29</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="69">
@@ -1766,11 +1766,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>71256.27</v>
+        <v>862.54</v>
       </c>
     </row>
     <row r="70">
@@ -1781,11 +1781,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>16564.71</v>
+        <v>43353.09</v>
       </c>
     </row>
     <row r="71">
@@ -1796,11 +1796,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>63650.71000000001</v>
+        <v>102813.61</v>
       </c>
     </row>
     <row r="72">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>22462.91</v>
+        <v>27593.63</v>
       </c>
     </row>
     <row r="73">
@@ -1826,11 +1826,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6826.26</v>
+        <v>64264.11</v>
       </c>
     </row>
     <row r="74">
@@ -1841,11 +1841,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2510.86</v>
+        <v>24095.51</v>
       </c>
     </row>
     <row r="75">
@@ -1856,56 +1856,56 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.02</v>
+        <v>9047.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>6276.88</v>
+        <v>1808.9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1815.59</v>
+        <v>2983.76</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>29.95</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="79">
@@ -1916,11 +1916,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3509.9</v>
+        <v>727.54</v>
       </c>
     </row>
     <row r="80">
@@ -1931,11 +1931,101 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>FAVORITA</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>6276.88</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GOLLOG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>8805.059999999999</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9249.43</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9147.969999999999</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>3509.9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>MAGALU</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="C85" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>R3 TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>157.53</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1542456.16</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>43.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3857193.38</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>8.890000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3829611.7</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>2493334.69</v>
       </c>
       <c r="D6" t="n">
-        <v>527678.1</v>
+        <v>527493.6</v>
       </c>
       <c r="E6" t="n">
-        <v>13.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5747075.1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>2261706.61</v>
@@ -567,7 +567,7 @@
         <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17756400.59</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>1568692.59</v>
       </c>
       <c r="D8" t="n">
-        <v>509866.83</v>
+        <v>508446.93</v>
       </c>
       <c r="E8" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36731164.22</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>1613646.39</v>
       </c>
       <c r="D9" t="n">
-        <v>277912.15</v>
+        <v>276329.63</v>
       </c>
       <c r="E9" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16611703.23</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1839372.09</v>
+        <v>1843737.19</v>
       </c>
       <c r="D10" t="n">
-        <v>37874.32</v>
+        <v>37080.32</v>
       </c>
       <c r="E10" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4417322.52</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>266298.55</v>
@@ -642,9 +642,7 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -653,7 +651,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8395809.18</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>120179.81</v>
@@ -661,9 +659,7 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -672,7 +668,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6075830.56</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>155603.53</v>
@@ -680,9 +676,7 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -691,7 +685,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3263554.56</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>143993.96</v>
@@ -699,9 +693,7 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -710,7 +702,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4468719.48</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>153281.8</v>
@@ -718,9 +710,7 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1275,7 +1265,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>154970.74</v>
+        <v>154786.24</v>
       </c>
     </row>
     <row r="37">
@@ -1665,7 +1655,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>120061.86</v>
+        <v>119941.86</v>
       </c>
     </row>
     <row r="63">
@@ -1680,7 +1670,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>42942.7</v>
+        <v>41642.8</v>
       </c>
     </row>
     <row r="64">
@@ -1785,7 +1775,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>43353.09</v>
+        <v>43265.27</v>
       </c>
     </row>
     <row r="71">
@@ -1800,7 +1790,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>102813.61</v>
+        <v>102795.51</v>
       </c>
     </row>
     <row r="72">
@@ -1815,7 +1805,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>27593.63</v>
+        <v>26293.73</v>
       </c>
     </row>
     <row r="73">
@@ -1845,7 +1835,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>24095.51</v>
+        <v>23918.81</v>
       </c>
     </row>
     <row r="75">
@@ -1950,7 +1940,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8805.059999999999</v>
+        <v>8011.06</v>
       </c>
     </row>
     <row r="82">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>47477011.06</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>35369445.9</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>48202341.66</v>
       </c>
       <c r="C6" t="n">
         <v>2493334.69</v>
@@ -548,7 +548,7 @@
         <v>527493.6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>45619009.1</v>
       </c>
       <c r="C7" t="n">
         <v>2261706.61</v>
@@ -567,7 +567,7 @@
         <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>35512801.18</v>
       </c>
       <c r="C8" t="n">
         <v>1568692.59</v>
@@ -586,7 +586,7 @@
         <v>508446.93</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="9">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>73462328.44</v>
       </c>
       <c r="C9" t="n">
         <v>1613646.39</v>
@@ -605,7 +605,7 @@
         <v>276329.63</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>50574650.66</v>
       </c>
       <c r="C10" t="n">
         <v>1843737.19</v>
       </c>
       <c r="D10" t="n">
-        <v>37080.32</v>
+        <v>36960.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>10108486.05</v>
       </c>
       <c r="C11" t="n">
         <v>266298.55</v>
@@ -642,7 +642,9 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -651,7 +653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>16791618.36</v>
       </c>
       <c r="C12" t="n">
         <v>120179.81</v>
@@ -659,7 +661,9 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -668,7 +672,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>12151661.12</v>
       </c>
       <c r="C13" t="n">
         <v>155603.53</v>
@@ -676,7 +680,9 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -685,7 +691,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6527109.12</v>
       </c>
       <c r="C14" t="n">
         <v>143993.96</v>
@@ -693,7 +699,9 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -702,7 +710,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8937438.960000001</v>
       </c>
       <c r="C15" t="n">
         <v>153281.8</v>
@@ -710,7 +718,9 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1940,7 +1950,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8011.06</v>
+        <v>7891.16</v>
       </c>
     </row>
     <row r="82">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47477011.06</v>
+        <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35369445.9</v>
+        <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48202341.66</v>
+        <v>33077113.66</v>
       </c>
       <c r="C6" t="n">
         <v>2493334.69</v>
@@ -548,7 +548,7 @@
         <v>527493.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45619009.1</v>
+        <v>27272055.46</v>
       </c>
       <c r="C7" t="n">
         <v>2261706.61</v>
@@ -567,7 +567,7 @@
         <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1.14</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35512801.18</v>
+        <v>17094736.84</v>
       </c>
       <c r="C8" t="n">
         <v>1568692.59</v>
@@ -586,7 +586,7 @@
         <v>508446.93</v>
       </c>
       <c r="E8" t="n">
-        <v>1.43</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="9">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73462328.44</v>
+        <v>29888833.67</v>
       </c>
       <c r="C9" t="n">
         <v>1613646.39</v>
@@ -605,7 +605,7 @@
         <v>276329.63</v>
       </c>
       <c r="E9" t="n">
-        <v>0.38</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50574650.66</v>
+        <v>27089063.61</v>
       </c>
       <c r="C10" t="n">
         <v>1843737.19</v>
@@ -624,7 +624,7 @@
         <v>36960.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10108486.05</v>
+        <v>1273841.01</v>
       </c>
       <c r="C11" t="n">
         <v>266298.55</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16791618.36</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>120179.81</v>
@@ -661,9 +661,7 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -672,7 +670,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12151661.12</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>155603.53</v>
@@ -680,9 +678,7 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -691,7 +687,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6527109.12</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>143993.96</v>
@@ -699,9 +695,7 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -710,7 +704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8937438.960000001</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>153281.8</v>
@@ -718,9 +712,7 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -602,7 +602,7 @@
         <v>1613646.39</v>
       </c>
       <c r="D9" t="n">
-        <v>276329.63</v>
+        <v>276153.51</v>
       </c>
       <c r="E9" t="n">
         <v>0.92</v>
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>102795.51</v>
+        <v>102619.39</v>
       </c>
     </row>
     <row r="72">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37825043.31</v>
+        <v>1542456.16</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.79</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31158805.85</v>
+        <v>3857193.38</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33077113.66</v>
+        <v>3829611.7</v>
       </c>
       <c r="C6" t="n">
         <v>2493334.69</v>
@@ -548,7 +548,7 @@
         <v>527493.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.59</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27272055.46</v>
+        <v>5747075.1</v>
       </c>
       <c r="C7" t="n">
         <v>2261706.61</v>
@@ -567,7 +567,7 @@
         <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1.91</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17094736.84</v>
+        <v>17756400.59</v>
       </c>
       <c r="C8" t="n">
         <v>1568692.59</v>
@@ -586,7 +586,7 @@
         <v>508446.93</v>
       </c>
       <c r="E8" t="n">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="9">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29888833.67</v>
+        <v>36731164.22</v>
       </c>
       <c r="C9" t="n">
         <v>1613646.39</v>
@@ -605,7 +605,7 @@
         <v>276153.51</v>
       </c>
       <c r="E9" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27089063.61</v>
+        <v>39911427.77</v>
       </c>
       <c r="C10" t="n">
         <v>1843737.19</v>
@@ -624,7 +624,7 @@
         <v>36960.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1273841.01</v>
+        <v>5691163.53</v>
       </c>
       <c r="C11" t="n">
         <v>266298.55</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>8395809.18</v>
       </c>
       <c r="C12" t="n">
         <v>120179.81</v>
@@ -661,7 +661,9 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -670,7 +672,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>6075830.56</v>
       </c>
       <c r="C13" t="n">
         <v>155603.53</v>
@@ -678,7 +680,9 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -687,7 +691,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>4099324.42</v>
       </c>
       <c r="C14" t="n">
         <v>143993.96</v>
@@ -695,7 +699,9 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -704,7 +710,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5562976.36</v>
       </c>
       <c r="C15" t="n">
         <v>153281.8</v>
@@ -712,7 +718,9 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1542456.16</v>
+        <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>43.87</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3857193.38</v>
+        <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>8.890000000000001</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3829611.7</v>
+        <v>33077113.66</v>
       </c>
       <c r="C6" t="n">
         <v>2493334.69</v>
@@ -548,7 +548,7 @@
         <v>527493.6</v>
       </c>
       <c r="E6" t="n">
-        <v>13.77</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5747075.1</v>
+        <v>27272055.46</v>
       </c>
       <c r="C7" t="n">
         <v>2261706.61</v>
@@ -567,7 +567,7 @@
         <v>521010.6</v>
       </c>
       <c r="E7" t="n">
-        <v>9.07</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17756400.59</v>
+        <v>33290828.25</v>
       </c>
       <c r="C8" t="n">
         <v>1568692.59</v>
@@ -586,7 +586,7 @@
         <v>508446.93</v>
       </c>
       <c r="E8" t="n">
-        <v>2.86</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="9">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36731164.22</v>
+        <v>29888833.67</v>
       </c>
       <c r="C9" t="n">
         <v>1613646.39</v>
@@ -605,7 +605,7 @@
         <v>276153.51</v>
       </c>
       <c r="E9" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39911427.77</v>
+        <v>33037543.95</v>
       </c>
       <c r="C10" t="n">
         <v>1843737.19</v>
@@ -624,7 +624,7 @@
         <v>36960.42</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5691163.53</v>
+        <v>1273841.01</v>
       </c>
       <c r="C11" t="n">
         <v>266298.55</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8395809.18</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>120179.81</v>
@@ -661,9 +661,7 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -672,7 +670,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6075830.56</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>155603.53</v>
@@ -680,9 +678,7 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -691,7 +687,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4099324.42</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>143993.96</v>
@@ -699,9 +695,7 @@
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -710,7 +704,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5562976.36</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>153281.8</v>
@@ -718,9 +712,7 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37825043.31</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31158805.85</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33077113.66</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>2493334.69</v>
+        <v>2495260.41</v>
       </c>
       <c r="D6" t="n">
-        <v>527493.6</v>
+        <v>528824.0600000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27272055.46</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2261706.61</v>
+        <v>2287728.2</v>
       </c>
       <c r="D7" t="n">
-        <v>521010.6</v>
+        <v>527822.29</v>
       </c>
       <c r="E7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33290828.25</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>1568692.59</v>
+        <v>1577107.63</v>
       </c>
       <c r="D8" t="n">
-        <v>508446.93</v>
+        <v>537278.86</v>
       </c>
       <c r="E8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29888833.67</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1613646.39</v>
+        <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>276153.51</v>
+        <v>375242.49</v>
       </c>
       <c r="E9" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33037543.95</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1843737.19</v>
+        <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>36960.42</v>
+        <v>123384.81</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -634,17 +634,15 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1273841.01</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>266298.55</v>
+        <v>823915.8100000001</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -673,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>155603.53</v>
+        <v>170926.23</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -690,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>143993.96</v>
+        <v>159740.91</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -707,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>153281.8</v>
+        <v>569718.16</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -725,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1338,11 +1336,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>11346.63</v>
+        <v>1330.46</v>
       </c>
     </row>
     <row r="42">
@@ -1353,11 +1351,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6009.39</v>
+        <v>11346.63</v>
       </c>
     </row>
     <row r="43">
@@ -1368,26 +1366,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3440.8</v>
+        <v>6009.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>558.48</v>
+        <v>3440.8</v>
       </c>
     </row>
     <row r="45">
@@ -1398,11 +1396,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3205.82</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="46">
@@ -1413,11 +1411,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>22805.01</v>
+        <v>3205.82</v>
       </c>
     </row>
     <row r="47">
@@ -1428,11 +1426,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>50068.36</v>
+        <v>22805.01</v>
       </c>
     </row>
     <row r="48">
@@ -1443,11 +1441,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>226650.61</v>
+        <v>50068.36</v>
       </c>
     </row>
     <row r="49">
@@ -1458,11 +1456,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>23648.49</v>
+        <v>231249.33</v>
       </c>
     </row>
     <row r="50">
@@ -1473,11 +1471,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>64840.81</v>
+        <v>25662.51</v>
       </c>
     </row>
     <row r="51">
@@ -1488,11 +1486,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>59516.32</v>
+        <v>64840.81</v>
       </c>
     </row>
     <row r="52">
@@ -1503,11 +1501,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>52391.37</v>
+        <v>59715.27</v>
       </c>
     </row>
     <row r="53">
@@ -1518,11 +1516,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>767</v>
+        <v>52391.37</v>
       </c>
     </row>
     <row r="54">
@@ -1533,11 +1531,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>15210.43</v>
+        <v>767</v>
       </c>
     </row>
     <row r="55">
@@ -1548,26 +1546,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1347.9</v>
+        <v>15210.43</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>7161.53</v>
+        <v>1347.9</v>
       </c>
     </row>
     <row r="57">
@@ -1578,11 +1576,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7009</v>
+        <v>7161.53</v>
       </c>
     </row>
     <row r="58">
@@ -1593,11 +1591,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6757.07</v>
+        <v>7009</v>
       </c>
     </row>
     <row r="59">
@@ -1608,11 +1606,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>27222.1</v>
+        <v>6757.07</v>
       </c>
     </row>
     <row r="60">
@@ -1623,11 +1621,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>214668.87</v>
+        <v>27222.1</v>
       </c>
     </row>
     <row r="61">
@@ -1638,11 +1636,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>70353.68000000001</v>
+        <v>237492.1</v>
       </c>
     </row>
     <row r="62">
@@ -1653,11 +1651,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>119941.86</v>
+        <v>71895.68000000001</v>
       </c>
     </row>
     <row r="63">
@@ -1668,11 +1666,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41642.8</v>
+        <v>121234.73</v>
       </c>
     </row>
     <row r="64">
@@ -1683,11 +1681,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11880.01</v>
+        <v>44816.63</v>
       </c>
     </row>
     <row r="65">
@@ -1698,26 +1696,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1810.01</v>
+        <v>11880.01</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>96.63</v>
+        <v>1810.01</v>
       </c>
     </row>
     <row r="67">
@@ -1728,11 +1726,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>906.5</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="68">
@@ -1743,11 +1741,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>86.45</v>
+        <v>906.5</v>
       </c>
     </row>
     <row r="69">
@@ -1758,11 +1756,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>862.54</v>
+        <v>171.83</v>
       </c>
     </row>
     <row r="70">
@@ -1773,11 +1771,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>43265.27</v>
+        <v>639.36</v>
       </c>
     </row>
     <row r="71">
@@ -1788,11 +1786,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>102619.39</v>
+        <v>1260.88</v>
       </c>
     </row>
     <row r="72">
@@ -1803,11 +1801,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>26293.73</v>
+        <v>46281.09</v>
       </c>
     </row>
     <row r="73">
@@ -1818,11 +1816,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>64264.11</v>
+        <v>175203.39</v>
       </c>
     </row>
     <row r="74">
@@ -1833,11 +1831,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>23918.81</v>
+        <v>43112.77</v>
       </c>
     </row>
     <row r="75">
@@ -1848,11 +1846,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9047.4</v>
+        <v>68438.01000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1863,11 +1861,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1808.9</v>
+        <v>24483.29</v>
       </c>
     </row>
     <row r="77">
@@ -1878,11 +1876,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2983.76</v>
+        <v>9598.15</v>
       </c>
     </row>
     <row r="78">
@@ -1893,41 +1891,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.02</v>
+        <v>1906.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>727.54</v>
+        <v>3143.76</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>6276.88</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="81">
@@ -1938,11 +1936,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7891.16</v>
+        <v>7445.400000000001</v>
       </c>
     </row>
     <row r="82">
@@ -1953,11 +1951,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9249.43</v>
+        <v>607.13</v>
       </c>
     </row>
     <row r="83">
@@ -1968,11 +1966,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9147.969999999999</v>
+        <v>6276.88</v>
       </c>
     </row>
     <row r="84">
@@ -1983,11 +1981,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3509.9</v>
+        <v>9478.23</v>
       </c>
     </row>
     <row r="85">
@@ -1998,11 +1996,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>0.01</v>
+        <v>33566.44</v>
       </c>
     </row>
     <row r="86">
@@ -2013,10 +2011,70 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>10423.88</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>42943.54</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>12485.77</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PACÍFICO</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>R3 TRANSPORTES</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="C90" t="n">
         <v>157.53</v>
       </c>
     </row>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
         <v>2153017.43</v>
@@ -510,7 +510,7 @@
         <v>676735.1900000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
         <v>2482598.59</v>
@@ -529,7 +529,7 @@
         <v>342778.37</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>33077113.66</v>
       </c>
       <c r="C6" t="n">
         <v>2495260.41</v>
@@ -548,7 +548,7 @@
         <v>528824.0600000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>27272055.46</v>
       </c>
       <c r="C7" t="n">
         <v>2287728.2</v>
@@ -567,7 +567,7 @@
         <v>527822.29</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>33290828.25</v>
       </c>
       <c r="C8" t="n">
         <v>1577107.63</v>
@@ -586,7 +586,7 @@
         <v>537278.86</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="9">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>29888833.67</v>
       </c>
       <c r="C9" t="n">
         <v>1621122.95</v>
@@ -605,7 +605,7 @@
         <v>375242.49</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="10">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>33033084.91</v>
       </c>
       <c r="C10" t="n">
         <v>1870761.69</v>
@@ -624,7 +624,7 @@
         <v>123384.81</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="11">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>19970931.83</v>
       </c>
       <c r="C11" t="n">
         <v>823915.8100000001</v>
@@ -642,7 +642,9 @@
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -507,7 +507,7 @@
         <v>2153017.43</v>
       </c>
       <c r="D4" t="n">
-        <v>676735.1900000001</v>
+        <v>676771.64</v>
       </c>
       <c r="E4" t="n">
         <v>1.79</v>
@@ -564,10 +564,10 @@
         <v>2287728.2</v>
       </c>
       <c r="D7" t="n">
-        <v>527822.29</v>
+        <v>516323.24</v>
       </c>
       <c r="E7" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8">
@@ -583,7 +583,7 @@
         <v>1577107.63</v>
       </c>
       <c r="D8" t="n">
-        <v>537278.86</v>
+        <v>537522.62</v>
       </c>
       <c r="E8" t="n">
         <v>1.61</v>
@@ -602,10 +602,10 @@
         <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>375242.49</v>
+        <v>396087.56</v>
       </c>
       <c r="E9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="10">
@@ -621,10 +621,10 @@
         <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>123384.81</v>
+        <v>149746.61</v>
       </c>
       <c r="E10" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="11">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19970931.83</v>
+        <v>26797887.82</v>
       </c>
       <c r="C11" t="n">
-        <v>823915.8100000001</v>
+        <v>1268620.3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93867.53</v>
+        <v>93903.98</v>
       </c>
     </row>
     <row r="19">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>50068.36</v>
+        <v>38569.31</v>
       </c>
     </row>
     <row r="49">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>237492.1</v>
+        <v>237735.86</v>
       </c>
     </row>
     <row r="62">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>46281.09</v>
+        <v>34782.03</v>
       </c>
     </row>
     <row r="73">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>175203.39</v>
+        <v>202807.39</v>
       </c>
     </row>
     <row r="74">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>43112.77</v>
+        <v>47693.08</v>
       </c>
     </row>
     <row r="75">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>24483.29</v>
+        <v>24643.09</v>
       </c>
     </row>
     <row r="77">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9598.15</v>
+        <v>9598.17</v>
       </c>
     </row>
     <row r="78">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>7445.400000000001</v>
+        <v>8948.299999999999</v>
       </c>
     </row>
     <row r="82">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>33566.44</v>
+        <v>54378.63</v>
       </c>
     </row>
     <row r="86">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10423.88</v>
+        <v>10933.88</v>
       </c>
     </row>
     <row r="87">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12485.77</v>
+        <v>12485.79</v>
       </c>
     </row>
     <row r="89">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>157.53</v>
+        <v>3694.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -602,7 +602,7 @@
         <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>396087.56</v>
+        <v>396087.54</v>
       </c>
       <c r="E9" t="n">
         <v>1.33</v>
@@ -621,10 +621,10 @@
         <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>149746.61</v>
+        <v>337796.01</v>
       </c>
       <c r="E10" t="n">
-        <v>0.45</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="11">
@@ -640,10 +640,10 @@
         <v>1268620.3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>39270.78</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9598.17</v>
+        <v>9598.15</v>
       </c>
     </row>
     <row r="78">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8948.299999999999</v>
+        <v>23280.72</v>
       </c>
     </row>
     <row r="82">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>607.13</v>
+        <v>9825.09</v>
       </c>
     </row>
     <row r="83">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>6276.88</v>
+        <v>182.58</v>
       </c>
     </row>
     <row r="84">
@@ -1983,11 +1983,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9478.23</v>
+        <v>11262.13</v>
       </c>
     </row>
     <row r="85">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>54378.63</v>
+        <v>40258.65</v>
       </c>
     </row>
     <row r="86">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10933.88</v>
+        <v>134677.16</v>
       </c>
     </row>
     <row r="87">
@@ -2028,11 +2028,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>42943.54</v>
+        <v>31605.58</v>
       </c>
     </row>
     <row r="88">
@@ -2043,11 +2043,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12485.79</v>
+        <v>44513.44</v>
       </c>
     </row>
     <row r="89">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>LSP</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>0.01</v>
+        <v>217.62</v>
       </c>
     </row>
     <row r="90">
@@ -2073,11 +2073,161 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>35393.39</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PACÍFICO</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>R3 TRANSPORTES</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>3694.22</v>
+      <c r="C92" t="n">
+        <v>5780.64</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>STONE ENTREGA</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ASAPLOG</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1017.84</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GOLLOG</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>13009.58</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>16019.88</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1409.13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>6867.01</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>397.35</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>R3 TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>549.99</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -602,10 +602,10 @@
         <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>396087.54</v>
+        <v>395925.94</v>
       </c>
       <c r="E9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="10">
@@ -621,7 +621,7 @@
         <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>337796.01</v>
+        <v>337457.01</v>
       </c>
       <c r="E10" t="n">
         <v>1.02</v>
@@ -640,7 +640,7 @@
         <v>1268620.3</v>
       </c>
       <c r="D11" t="n">
-        <v>39270.78</v>
+        <v>39033.45</v>
       </c>
       <c r="E11" t="n">
         <v>0.15</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>202807.39</v>
+        <v>202645.79</v>
       </c>
     </row>
     <row r="74">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>134677.16</v>
+        <v>134338.16</v>
       </c>
     </row>
     <row r="87">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1017.84</v>
+        <v>780.51</v>
       </c>
     </row>
     <row r="95">

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -564,7 +564,7 @@
         <v>2287728.2</v>
       </c>
       <c r="D7" t="n">
-        <v>516323.24</v>
+        <v>516773.74</v>
       </c>
       <c r="E7" t="n">
         <v>1.89</v>
@@ -583,10 +583,10 @@
         <v>1577107.63</v>
       </c>
       <c r="D8" t="n">
-        <v>537522.62</v>
+        <v>538346.92</v>
       </c>
       <c r="E8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>395925.94</v>
+        <v>404822.2</v>
       </c>
       <c r="E9" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="10">
@@ -621,10 +621,10 @@
         <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>337457.01</v>
+        <v>373454.49</v>
       </c>
       <c r="E10" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="11">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26797887.82</v>
+        <v>35068190.93</v>
       </c>
       <c r="C11" t="n">
-        <v>1268620.3</v>
+        <v>1677260.43</v>
       </c>
       <c r="D11" t="n">
-        <v>39033.45</v>
+        <v>62832.93</v>
       </c>
       <c r="E11" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12">
@@ -725,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>22805.01</v>
+        <v>23190.51</v>
       </c>
     </row>
     <row r="48">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>231249.33</v>
+        <v>231314.33</v>
       </c>
     </row>
     <row r="50">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>237735.86</v>
+        <v>238560.16</v>
       </c>
     </row>
     <row r="62">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>34782.03</v>
+        <v>35469.43</v>
       </c>
     </row>
     <row r="73">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>202645.79</v>
+        <v>207107.78</v>
       </c>
     </row>
     <row r="74">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>47693.08</v>
+        <v>51439.95</v>
       </c>
     </row>
     <row r="75">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>23280.72</v>
+        <v>31615.14</v>
       </c>
     </row>
     <row r="82">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11262.13</v>
+        <v>11296.13</v>
       </c>
     </row>
     <row r="85">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>134338.16</v>
+        <v>147056.32</v>
       </c>
     </row>
     <row r="87">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>31605.58</v>
+        <v>33896.08</v>
       </c>
     </row>
     <row r="88">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>44513.44</v>
+        <v>46297.39</v>
       </c>
     </row>
     <row r="89">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>217.62</v>
+        <v>717.61</v>
       </c>
     </row>
     <row r="90">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>35393.39</v>
+        <v>45729.85</v>
       </c>
     </row>
     <row r="91">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>ANJUN EXPRESS</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>780.51</v>
+        <v>203.7</v>
       </c>
     </row>
     <row r="95">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>13009.58</v>
+        <v>2072.41</v>
       </c>
     </row>
     <row r="96">
@@ -2163,11 +2163,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>16019.88</v>
+        <v>12941.13</v>
       </c>
     </row>
     <row r="97">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1409.13</v>
+        <v>25195.69</v>
       </c>
     </row>
     <row r="98">
@@ -2193,11 +2193,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>6867.01</v>
+        <v>2669.01</v>
       </c>
     </row>
     <row r="99">
@@ -2208,11 +2208,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>397.35</v>
+        <v>8927.030000000001</v>
       </c>
     </row>
     <row r="100">
@@ -2223,11 +2223,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>7322.3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>R3 TRANSPORTES</t>
         </is>
       </c>
-      <c r="C100" t="n">
-        <v>549.99</v>
+      <c r="C101" t="n">
+        <v>3501.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -507,10 +507,10 @@
         <v>2153017.43</v>
       </c>
       <c r="D4" t="n">
-        <v>676771.64</v>
+        <v>982700.05</v>
       </c>
       <c r="E4" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -526,10 +526,10 @@
         <v>2482598.59</v>
       </c>
       <c r="D5" t="n">
-        <v>342778.37</v>
+        <v>702140.8199999999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="6">
@@ -545,10 +545,10 @@
         <v>2495260.41</v>
       </c>
       <c r="D6" t="n">
-        <v>528824.0600000001</v>
+        <v>641916.39</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         <v>2287728.2</v>
       </c>
       <c r="D7" t="n">
-        <v>516773.74</v>
+        <v>633312.34</v>
       </c>
       <c r="E7" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="8">
@@ -583,10 +583,10 @@
         <v>1577107.63</v>
       </c>
       <c r="D8" t="n">
-        <v>538346.92</v>
+        <v>561603.79</v>
       </c>
       <c r="E8" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
@@ -602,10 +602,10 @@
         <v>1621122.95</v>
       </c>
       <c r="D9" t="n">
-        <v>404822.2</v>
+        <v>430441.2</v>
       </c>
       <c r="E9" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="10">
@@ -621,10 +621,10 @@
         <v>1870761.69</v>
       </c>
       <c r="D10" t="n">
-        <v>373454.49</v>
+        <v>469572.52</v>
       </c>
       <c r="E10" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="11">
@@ -640,10 +640,10 @@
         <v>1677260.43</v>
       </c>
       <c r="D11" t="n">
-        <v>62832.93</v>
+        <v>172447.63</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="12">
@@ -659,9 +659,11 @@
         <v>120179.81</v>
       </c>
       <c r="D12" t="n">
+        <v>430.73</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -676,9 +678,11 @@
         <v>170926.23</v>
       </c>
       <c r="D13" t="n">
+        <v>1009.86</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -693,9 +697,11 @@
         <v>159740.91</v>
       </c>
       <c r="D14" t="n">
+        <v>809.97</v>
+      </c>
+      <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -710,9 +716,11 @@
         <v>569718.16</v>
       </c>
       <c r="D15" t="n">
+        <v>39643.94</v>
+      </c>
+      <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -725,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,11 +911,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>199</v>
+        <v>371.92</v>
       </c>
     </row>
     <row r="13">
@@ -918,11 +926,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>AMAZON.COM.BR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>400.52</v>
+        <v>2084.5</v>
       </c>
     </row>
     <row r="14">
@@ -933,11 +941,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>AZUL CARGO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>633.42</v>
+        <v>2088.17</v>
       </c>
     </row>
     <row r="15">
@@ -948,11 +956,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>239522.81</v>
+        <v>22419.47</v>
       </c>
     </row>
     <row r="16">
@@ -963,11 +971,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>CARRIERS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>223997.96</v>
+        <v>292.8</v>
       </c>
     </row>
     <row r="17">
@@ -978,11 +986,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>48716.99</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18">
@@ -993,11 +1001,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>93903.98</v>
+        <v>1862.11</v>
       </c>
     </row>
     <row r="19">
@@ -1008,11 +1016,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66409.63</v>
+        <v>2089.69</v>
       </c>
     </row>
     <row r="20">
@@ -1023,1202 +1031,1202 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2987.33</v>
+        <v>1262.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4213.25</v>
+        <v>400.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15282.46</v>
+        <v>633.42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1570.5</v>
+        <v>318660.07</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>159369.52</v>
+        <v>270839.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>33484.54</v>
+        <v>50405.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>32391.74</v>
+        <v>168176.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>51090.22</v>
+        <v>83368.53999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>R3 EXPRESS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35914.24</v>
+        <v>1656.04</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5241.9</v>
+        <v>1653.13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>SHOPEE EXPRESS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4220</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>281.8</v>
+        <v>2987.33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6411.5</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>AZUL CARGO</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1336.8</v>
+        <v>87.84999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18497.71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>23867.46</v>
+        <v>4213.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>154786.24</v>
+        <v>13780.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1256.9</v>
+        <v>542.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>120780.84</v>
+        <v>15282.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>88884.27</v>
+        <v>1570.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>90593.25999999999</v>
+        <v>209880.76</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1330.46</v>
+        <v>81376.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11346.63</v>
+        <v>42578.01</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6009.39</v>
+        <v>83954.46000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3440.8</v>
+        <v>80742.57000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>R3 EXPRESS</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>558.48</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3205.82</v>
+        <v>9758.43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>23190.51</v>
+        <v>5241.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>TODOBRASIL</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38569.31</v>
+        <v>654.1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>231314.33</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>25662.51</v>
+        <v>1258.87</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>64840.81</v>
+        <v>250.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59715.27</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>52391.37</v>
+        <v>19096.44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>767</v>
+        <v>904.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>15210.43</v>
+        <v>1336.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1347.9</v>
+        <v>18497.71</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7161.53</v>
+        <v>23867.46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7009</v>
+        <v>163082.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6757.07</v>
+        <v>39958.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>27222.1</v>
+        <v>123678.84</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>238560.16</v>
+        <v>103654.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>71895.68000000001</v>
+        <v>91164.74000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MERCADO LIVRE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>121234.73</v>
+        <v>1450.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>44816.63</v>
+        <v>1330.46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>PAJUCARA</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>11880.01</v>
+        <v>1139.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1810.01</v>
+        <v>21326.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>SHOPEE EXPRESS</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>96.63</v>
+        <v>2628.95</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>906.5</v>
+        <v>6009.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>TODOBRASIL</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>171.83</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>639.36</v>
+        <v>3440.8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1260.88</v>
+        <v>851</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>35469.43</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>207107.78</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>51439.95</v>
+        <v>62318.97</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>68438.01000000001</v>
+        <v>1927.5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>24643.09</v>
+        <v>3205.82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9598.15</v>
+        <v>23190.51</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1906.81</v>
+        <v>38569.31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3143.76</v>
+        <v>235243.66</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.02</v>
+        <v>29887.01</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>31615.14</v>
+        <v>64840.81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9825.09</v>
+        <v>66530.63</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>182.58</v>
+        <v>52391.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>MELIATRUS</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>11296.13</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>40258.65</v>
+        <v>767</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>147056.32</v>
+        <v>16060.28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>STONE</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>33896.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>46297.39</v>
+        <v>1347.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LSP</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>717.61</v>
+        <v>1250.61</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>45729.85</v>
+        <v>7161.53</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0.01</v>
+        <v>12284.09</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5780.64</v>
+        <v>791</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STONE ENTREGA</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>799</v>
+        <v>7009</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ANJUN EXPRESS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>203.7</v>
+        <v>6757.07</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2072.41</v>
+        <v>27222.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>12941.13</v>
+        <v>239123.66</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>25195.69</v>
+        <v>6459.9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2669.01</v>
+        <v>73009.78</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8927.030000000001</v>
+        <v>121454.43</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2227,22 +2235,952 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>7322.3</v>
+        <v>44816.63</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>R3 TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11880.01</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VIA PAJUCARA</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1810.01</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>586.7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ASAPLOG</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>96.63</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CARVALIMA</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>906.5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CORREIOS</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>7002.61</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ENVIABYBUS</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>639.36</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FAVORITA</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>1260.88</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GOLLOG</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>35469.43</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>207311.32</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>51439.95</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>68438.01000000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>40750.62</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>9883.049999999999</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PACÍFICO</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1906.81</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>R3 TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>3143.76</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VIA PAJUCARA</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>588.9499999999999</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ASAPLOG</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>31615.13</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ATRUS INTERMEDIACAO</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>318.72</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>AZUL CARGO</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>6640.28</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CARVALIMA</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>9825.09</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CORREIOS</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2559.3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CORREIOS SEDEX - 34028316000103</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>385.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>FAVORITA</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>11296.13</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GOLLOG</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>40258.65</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>147256.22</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>55603.78</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>46297.39</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>60854.32</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LSP</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>717.61</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>45729.85</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>PACÍFICO</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>R3 EXPRESS</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>R3 TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>5780.64</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SHOPEE EXPRESS</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>STONE ENTREGA</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>405.8</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ANJUN EXPRESS</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>203.7</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ASAPLOG</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2427.84</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AZUL CARGO</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>30361.08</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CORREIOS</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>4855.440000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>GOLLOG</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>12941.13</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>28563.71</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>35187.19</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JAMEF</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>8927.030000000001</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>33927.87</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>7322.31</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
         <is>
           <t>R3 TRANSPORTES</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="C149" t="n">
         <v>3501.66</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>134.5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>630.0599999999999</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>230.9</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>148.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>299.97</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AGILE</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>49.88</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ASAPLOG</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>293.54</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>AZUL CARGO</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>15386.88</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CORREIOS</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>972.3599999999999</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>IMILE</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>JADLOG</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>8099.8</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>JET</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>12707.48</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MAGALU</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/Base_Mensal.xlsx
+++ b/data/Base_Mensal.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,13 +504,13 @@
         <v>37825043.31</v>
       </c>
       <c r="C4" t="n">
-        <v>2153017.43</v>
+        <v>2066062.45</v>
       </c>
       <c r="D4" t="n">
-        <v>982700.05</v>
+        <v>980763.12</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="5">
@@ -523,13 +523,13 @@
         <v>31158805.85</v>
       </c>
       <c r="C5" t="n">
-        <v>2482598.59</v>
+        <v>2377184.6</v>
       </c>
       <c r="D5" t="n">
-        <v>702140.8199999999</v>
+        <v>683728.86</v>
       </c>
       <c r="E5" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="6">
@@ -542,10 +542,10 @@
         <v>33077113.66</v>
       </c>
       <c r="C6" t="n">
-        <v>2495260.41</v>
+        <v>2452772.97</v>
       </c>
       <c r="D6" t="n">
-        <v>641916.39</v>
+        <v>640719.0600000001</v>
       </c>
       <c r="E6" t="n">
         <v>1.94</v>
@@ -561,7 +561,7 @@
         <v>27272055.46</v>
       </c>
       <c r="C7" t="n">
-        <v>2287728.2</v>
+        <v>2210153.48</v>
       </c>
       <c r="D7" t="n">
         <v>633312.34</v>
@@ -580,13 +580,13 @@
         <v>33290828.25</v>
       </c>
       <c r="C8" t="n">
-        <v>1577107.63</v>
+        <v>2006402.99</v>
       </c>
       <c r="D8" t="n">
-        <v>561603.79</v>
+        <v>566406.1800000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -599,13 +599,13 @@
         <v>29888833.67</v>
       </c>
       <c r="C9" t="n">
-        <v>1621122.95</v>
+        <v>2052781.36</v>
       </c>
       <c r="D9" t="n">
-        <v>430441.2</v>
+        <v>440203.17</v>
       </c>
       <c r="E9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="10">
@@ -618,13 +618,13 @@
         <v>33033084.91</v>
       </c>
       <c r="C10" t="n">
-        <v>1870761.69</v>
+        <v>2090733.29</v>
       </c>
       <c r="D10" t="n">
-        <v>469572.52</v>
+        <v>489789.54</v>
       </c>
       <c r="E10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="11">
@@ -637,89 +637,13 @@
         <v>35068190.93</v>
       </c>
       <c r="C11" t="n">
-        <v>1677260.43</v>
+        <v>1938466.39</v>
       </c>
       <c r="D11" t="n">
-        <v>172447.63</v>
+        <v>208259.26</v>
       </c>
       <c r="E11" t="n">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>120179.81</v>
-      </c>
-      <c r="D12" t="n">
-        <v>430.73</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>170926.23</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1009.86</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>159740.91</v>
-      </c>
-      <c r="D14" t="n">
-        <v>809.97</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>569718.16</v>
-      </c>
-      <c r="D15" t="n">
-        <v>39643.94</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C163"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,11 +835,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>AMAZON.COM.BR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>371.92</v>
+        <v>2084.5</v>
       </c>
     </row>
     <row r="13">
@@ -926,11 +850,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMAZON.COM.BR</t>
+          <t>AZUL CARGO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2084.5</v>
+        <v>2088.17</v>
       </c>
     </row>
     <row r="14">
@@ -941,11 +865,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AZUL CARGO</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2088.17</v>
+        <v>22419.47</v>
       </c>
     </row>
     <row r="15">
@@ -956,11 +880,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>CARRIERS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22419.47</v>
+        <v>292.8</v>
       </c>
     </row>
     <row r="16">
@@ -971,11 +895,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CARRIERS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>292.8</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17">
@@ -986,11 +910,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>199</v>
+        <v>297.1</v>
       </c>
     </row>
     <row r="18">
@@ -1001,11 +925,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1862.11</v>
+        <v>2089.69</v>
       </c>
     </row>
     <row r="19">
@@ -1016,11 +940,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>EBB</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2089.69</v>
+        <v>1262.86</v>
       </c>
     </row>
     <row r="20">
@@ -1031,11 +955,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EBB</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1262.86</v>
+        <v>400.52</v>
       </c>
     </row>
     <row r="21">
@@ -1046,11 +970,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>400.52</v>
+        <v>633.42</v>
       </c>
     </row>
     <row r="22">
@@ -1061,11 +985,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>633.42</v>
+        <v>318660.07</v>
       </c>
     </row>
     <row r="23">
@@ -1076,11 +1000,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>318660.07</v>
+        <v>270839.6</v>
       </c>
     </row>
     <row r="24">
@@ -1091,11 +1015,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>270839.6</v>
+        <v>50405.57</v>
       </c>
     </row>
     <row r="25">
@@ -1106,11 +1030,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50405.57</v>
+        <v>168176.96</v>
       </c>
     </row>
     <row r="26">
@@ -1121,11 +1045,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>168176.96</v>
+        <v>83368.53999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1136,11 +1060,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>R3 EXPRESS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>83368.53999999999</v>
+        <v>1656.04</v>
       </c>
     </row>
     <row r="28">
@@ -1151,11 +1075,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R3 EXPRESS</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1656.04</v>
+        <v>1653.13</v>
       </c>
     </row>
     <row r="29">
@@ -1166,11 +1090,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>SHOPEE EXPRESS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1653.13</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="30">
@@ -1181,26 +1105,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SHOPEE EXPRESS</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>39.9</v>
+        <v>2987.33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2987.33</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="32">
@@ -1211,11 +1135,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>AZUL CARGO</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="33">
@@ -1226,11 +1150,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AZUL CARGO</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>87.84999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
@@ -1241,11 +1165,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>90</v>
+        <v>4213.25</v>
       </c>
     </row>
     <row r="35">
@@ -1256,11 +1180,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4213.25</v>
+        <v>2159.8</v>
       </c>
     </row>
     <row r="36">
@@ -1271,11 +1195,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>13780.2</v>
+        <v>542.4</v>
       </c>
     </row>
     <row r="37">
@@ -1286,11 +1210,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>542.4</v>
+        <v>15282.46</v>
       </c>
     </row>
     <row r="38">
@@ -1301,11 +1225,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15282.46</v>
+        <v>1570.5</v>
       </c>
     </row>
     <row r="39">
@@ -1316,11 +1240,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1570.5</v>
+        <v>209880.76</v>
       </c>
     </row>
     <row r="40">
@@ -1331,11 +1255,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>209880.76</v>
+        <v>81376.77</v>
       </c>
     </row>
     <row r="41">
@@ -1346,11 +1270,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>81376.77</v>
+        <v>42578.01</v>
       </c>
     </row>
     <row r="42">
@@ -1361,11 +1285,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>42578.01</v>
+        <v>83954.46000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1376,11 +1300,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>83954.46000000001</v>
+        <v>80742.57000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1391,11 +1315,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>R3 EXPRESS</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>80742.57000000001</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="45">
@@ -1406,11 +1330,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R3 EXPRESS</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>399.99</v>
+        <v>9758.43</v>
       </c>
     </row>
     <row r="46">
@@ -1421,11 +1345,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9758.43</v>
+        <v>5241.9</v>
       </c>
     </row>
     <row r="47">
@@ -1436,11 +1360,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>TODOBRASIL</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5241.9</v>
+        <v>654.1</v>
       </c>
     </row>
     <row r="48">
@@ -1451,26 +1375,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TODOBRASIL</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>654.1</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4220</v>
+        <v>152.8</v>
       </c>
     </row>
     <row r="50">
@@ -1481,11 +1405,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1258.87</v>
+        <v>250.25</v>
       </c>
     </row>
     <row r="51">
@@ -1496,11 +1420,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>250.25</v>
+        <v>281.8</v>
       </c>
     </row>
     <row r="52">
@@ -1511,11 +1435,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>281.8</v>
+        <v>19005.18</v>
       </c>
     </row>
     <row r="53">
@@ -1526,11 +1450,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>19096.44</v>
+        <v>904.75</v>
       </c>
     </row>
     <row r="54">
@@ -1541,11 +1465,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>904.75</v>
+        <v>1336.8</v>
       </c>
     </row>
     <row r="55">
@@ -1556,11 +1480,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1336.8</v>
+        <v>18497.71</v>
       </c>
     </row>
     <row r="56">
@@ -1571,11 +1495,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18497.71</v>
+        <v>23867.46</v>
       </c>
     </row>
     <row r="57">
@@ -1586,11 +1510,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>23867.46</v>
+        <v>163082.24</v>
       </c>
     </row>
     <row r="58">
@@ -1601,11 +1525,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>163082.24</v>
+        <v>39958.8</v>
       </c>
     </row>
     <row r="59">
@@ -1616,11 +1540,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39958.8</v>
+        <v>123678.84</v>
       </c>
     </row>
     <row r="60">
@@ -1631,11 +1555,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>123678.84</v>
+        <v>103654.04</v>
       </c>
     </row>
     <row r="61">
@@ -1646,11 +1570,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>103654.04</v>
+        <v>91164.74000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1661,11 +1585,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>MERCADO LIVRE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>91164.74000000001</v>
+        <v>1450.86</v>
       </c>
     </row>
     <row r="63">
@@ -1676,11 +1600,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MERCADO LIVRE</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1450.86</v>
+        <v>1330.46</v>
       </c>
     </row>
     <row r="64">
@@ -1691,11 +1615,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>PAJUCARA</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1330.46</v>
+        <v>1139.1</v>
       </c>
     </row>
     <row r="65">
@@ -1706,11 +1630,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PAJUCARA</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1139.1</v>
+        <v>21326.11</v>
       </c>
     </row>
     <row r="66">
@@ -1721,11 +1645,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>SHOPEE EXPRESS</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>21326.11</v>
+        <v>2628.95</v>
       </c>
     </row>
     <row r="67">
@@ -1736,11 +1660,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SHOPEE EXPRESS</t>
+          <t>TODO BRASIL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2628.95</v>
+        <v>6009.39</v>
       </c>
     </row>
     <row r="68">
@@ -1751,11 +1675,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TODO BRASIL</t>
+          <t>TODOBRASIL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>6009.39</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="69">
@@ -1766,26 +1690,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TODOBRASIL</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8250</v>
+        <v>3440.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3440.8</v>
+        <v>851</v>
       </c>
     </row>
     <row r="71">
@@ -1796,11 +1720,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>AZUL LINHAS AEREAS</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>851</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -1811,11 +1735,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AZUL LINHAS AEREAS</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>82.90000000000001</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="73">
@@ -1826,11 +1750,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>558.48</v>
+        <v>62318.97</v>
       </c>
     </row>
     <row r="74">
@@ -1841,11 +1765,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>62318.97</v>
+        <v>1927.5</v>
       </c>
     </row>
     <row r="75">
@@ -1856,11 +1780,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1927.5</v>
+        <v>3205.82</v>
       </c>
     </row>
     <row r="76">
@@ -1871,11 +1795,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3205.82</v>
+        <v>23190.51</v>
       </c>
     </row>
     <row r="77">
@@ -1886,11 +1810,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>23190.51</v>
+        <v>38569.31</v>
       </c>
     </row>
     <row r="78">
@@ -1901,11 +1825,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>38569.31</v>
+        <v>235243.66</v>
       </c>
     </row>
     <row r="79">
@@ -1916,11 +1840,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>235243.66</v>
+        <v>29887.01</v>
       </c>
     </row>
     <row r="80">
@@ -1931,11 +1855,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>29887.01</v>
+        <v>64840.81</v>
       </c>
     </row>
     <row r="81">
@@ -1946,11 +1870,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>64840.81</v>
+        <v>66530.63</v>
       </c>
     </row>
     <row r="82">
@@ -1961,11 +1885,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>66530.63</v>
+        <v>52391.37</v>
       </c>
     </row>
     <row r="83">
@@ -1976,11 +1900,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>MELIATRUS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>52391.37</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84">
@@ -1991,11 +1915,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MELIATRUS</t>
+          <t>PACÍFICO</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>169</v>
+        <v>767</v>
       </c>
     </row>
     <row r="85">
@@ -2006,11 +1930,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PACÍFICO</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>767</v>
+        <v>16060.28</v>
       </c>
     </row>
     <row r="86">
@@ -2021,11 +1945,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>STONE</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>16060.28</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="87">
@@ -2036,26 +1960,26 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STONE</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0.01</v>
+        <v>1347.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1347.9</v>
+        <v>1222.6</v>
       </c>
     </row>
     <row r="89">
@@ -2066,11 +1990,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>CARVALIMA</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1250.61</v>
+        <v>7161.53</v>
       </c>
     </row>
     <row r="90">
@@ -2081,11 +2005,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CARVALIMA</t>
+          <t>CORREIOS</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7161.53</v>
+        <v>16177.13</v>
       </c>
     </row>
     <row r="91">
@@ -2096,11 +2020,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CORREIOS</t>
+          <t>CORREIOS SEDEX - 34028316000103</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12284.09</v>
+        <v>791</v>
       </c>
     </row>
     <row r="92">
@@ -2111,11 +2035,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CORREIOS SEDEX - 34028316000103</t>
+          <t>ENVIABYBUS</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>791</v>
+        <v>7009</v>
       </c>
     </row>
     <row r="93">
@@ -2126,11 +2050,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ENVIABYBUS</t>
+          <t>FAVORITA</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>7009</v>
+        <v>6757.07</v>
       </c>
     </row>
     <row r="94">
@@ -2141,11 +2065,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FAVORITA</t>
+          <t>GOLLOG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>6757.07</v>
+        <v>27222.1</v>
       </c>
     </row>
     <row r="95">
@@ -2156,11 +2080,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GOLLOG</t>
+          <t>IMILE</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>27222.1</v>
+        <v>239932.06</v>
       </c>
     </row>
     <row r="96">
@@ -2171,11 +2095,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IMILE</t>
+          <t>JADLOG</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>239123.66</v>
+        <v>6459.9</v>
       </c>
     </row>
     <row r="97">
@@ -2186,11 +2110,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JADLOG</t>
+          <t>JAMEF</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6459.9</v>
+        <v>73009.78</v>
       </c>
     </row>
     <row r="98">
@@ -2201,11 +2125,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JAMEF</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>73009.78</v>
+        <v>121583.38</v>
       </c>
     </row>
     <row r="99">
@@ -2216,11 +2140,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JET</t>
+          <t>MAGALU</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>121454.43</v>
+        <v>44816.63</v>
       </c>
     </row>
     <row r="100">
@@ -2231,11 +2155,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAGALU</t>
+          <t>R3 TRANSPORTES</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>44816.63</v>
+        <v>11880.01</v>
       </c>
     </row>
     <row r="101">
@@ -2246,26 +2170,26 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>R3 TRANSPORTES</t>
+          <t>VIA PAJUCARA</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11880.01</v>
+        <v>1810.01</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VIA PAJUCARA</t>
+          <t>AGILE</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1810.01</v>
+        <v>2941.14</v>
       </c>
     </row>
     <row r="103">
@@ -2276,11 +2200,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AGILE</t>
+          <t>ASAPLOG</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>586.7</v>
+        <v>96.63</v>
       </c>
     </row>
     <row r="104">
@@ -2291,11 +2215,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ASAPLOG</t>
+          <t>AZUL CARGO</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>96.63</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="105">
@@ -2325,7 +2249,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7002.61</v>
+        <v>13917.5</v>
       </c>
     </row>
     <row r="107">
@@ -2385,7 +2309,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>207311.32</v>
+        <v>207716.42</v>
       </c>
     </row>
     <row r="111">
@@ -2400,7 +2324,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>51439.95</v>
+        <v>52121.95</v>
       </c>
     </row>
     <row r="112">
@@ -2430,7 +2354,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>40750.62</v>
+        <v>32432.82</v>
       </c>
     </row>
     <row r="114">
@@ -2505,7 +2429,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>588.9499999999999</v>
+        <v>685.78</v>
       </c>
     </row>
     <row r="119">
@@ -2520,7 +2444,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>31615.13</v>
+        <v>31639.13</v>
       </c>
     </row>
     <row r="120">
@@ -2580,7 +2504,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2559.3</v>
+        <v>8619.08</v>
       </c>
     </row>
     <row r="124">
@@ -2625,7 +2549,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>40258.65</v>
+        <v>43896.72</v>
       </c>
     </row>
     <row r="127">
@@ -2640,7 +2564,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>147256.22</v>
+        <v>147505.41</v>
       </c>
     </row>
     <row r="128">
@@ -2685,7 +2609,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>60854.32</v>
+        <v>69800.42</v>
       </c>
     </row>
     <row r="131">
@@ -2715,7 +2639,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>45729.85</v>
+        <v>46669.84</v>
       </c>
     </row>
     <row r="133">
@@ -2805,7 +2729,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>405.8</v>
+        <v>440.44</v>
       </c>
     </row>
     <row r="139">
@@ -2835,7 +2759,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>2427.84</v>
+        <v>2721.38</v>
       </c>
     </row>
     <row r="141">
@@ -2850,7 +2774,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>30361.08</v>
+        <v>46647.95</v>
       </c>
     </row>
     <row r="142">
@@ -2865,7 +2789,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4855.440000000001</v>
+        <v>2236.76</v>
       </c>
     </row>
     <row r="143">
@@ -2880,7 +2804,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>12941.13</v>
+        <v>13101.08</v>
       </c>
     </row>
     <row r="144">
@@ -2895,7 +2819,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>28563.71</v>
+        <v>28949.21</v>
       </c>
     </row>
     <row r="145">
@@ -2910,7 +2834,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>35187.19</v>
+        <v>43286.99</v>
       </c>
     </row>
     <row r="146">
@@ -2940,7 +2864,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>33927.87</v>
+        <v>46161.5</v>
       </c>
     </row>
     <row r="148">
@@ -2955,7 +2879,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>7322.31</v>
+        <v>7322.33</v>
       </c>
     </row>
     <row r="149">
@@ -2971,216 +2895,6 @@
       </c>
       <c r="C149" t="n">
         <v>3501.66</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>JADLOG</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>134.5</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>AGILE</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>630.0599999999999</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>IMILE</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>230.9</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>148.9</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>AGILE</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>299.97</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>AGILE</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>49.88</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>ASAPLOG</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>293.54</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>AZUL CARGO</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>15386.88</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>CORREIOS</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>972.3599999999999</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>IMILE</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>JADLOG</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>8099.8</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>JET</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>12707.48</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>MAGALU</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>0.02</v>
       </c>
     </row>
   </sheetData>
